--- a/public/po-template.xlsx
+++ b/public/po-template.xlsx
@@ -976,8 +976,8 @@
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="H5:K10"/>
   </mergeCells>
-  <drawing ns1:id="R8337dd9c878646a8"/>
   <pageMargins left="0.6" right="0.6" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
+  <drawing ns1:id="R8337dd9c878646a8"/>
 </worksheet>
 </file>